--- a/Incentive_Owner.xlsx
+++ b/Incentive_Owner.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Userdata\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Userdata\Desktop\AdmissionsDashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DFE8821-3FF7-466C-909B-2ACD1F734499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFEFF08-0C90-4F1F-B0BD-67C179E6EEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F0A3148F-155A-4468-9EDA-BCC93CBDFB99}"/>
   </bookViews>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>7</v>
       </c>
       <c r="I7" s="15">
-        <v>50000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
